--- a/Database_Basque_toponyms_ending_in_-ga.xlsx
+++ b/Database_Basque_toponyms_ending_in_-ga.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Contributions\Talks\To_be_given\2024\ICOS28_2024_The_Basque_locative_suffix_-ga_through_the_lens_of_onomastics\Database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C3AAA97-D7C4-4ECB-B107-502D14063E77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA1CA648-FE78-4734-982F-65A3AFF8FE2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3512" uniqueCount="1900">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3513" uniqueCount="1900">
   <si>
     <t>Toponym</t>
   </si>
@@ -35659,6 +35659,9 @@
       <c r="H286" s="4" t="s">
         <v>23</v>
       </c>
+      <c r="I286" s="4" t="s">
+        <v>23</v>
+      </c>
       <c r="J286" s="7" t="s">
         <v>1800</v>
       </c>
